--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2506,6 +2506,13 @@
         <v>277</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2517,7 +2524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4433,6 +4440,13 @@
       <c r="E108" s="3" t="n"/>
       <c r="F108" s="3" t="n">
         <v>129</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2513,6 +2513,26 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E110" s="3" t="n"/>
+      <c r="F110" s="3" t="n">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2524,7 +2544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4447,6 +4467,26 @@
         <is>
           <t>2026-09-13</t>
         </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="n">
+        <v>254</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E110" s="3" t="n"/>
+      <c r="F110" s="3" t="n">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F110"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2533,6 +2533,28 @@
         <v>33</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>234</v>
+      </c>
+      <c r="C111" t="n">
+        <v>91</v>
+      </c>
+      <c r="D111" t="n">
+        <v>30</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2</v>
+      </c>
+      <c r="F111" t="n">
+        <v>251</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2544,7 +2566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F110"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4487,6 +4509,25 @@
       <c r="E110" s="3" t="n"/>
       <c r="F110" s="3" t="n">
         <v>138</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>686</v>
+      </c>
+      <c r="C111" t="n">
+        <v>102</v>
+      </c>
+      <c r="D111" t="n">
+        <v>8</v>
+      </c>
+      <c r="F111" t="n">
+        <v>452</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F111"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2555,6 +2555,26 @@
         <v>251</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="E112" s="3" t="n"/>
+      <c r="F112" s="3" t="n">
+        <v>265</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2566,7 +2586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F111"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4528,6 +4548,28 @@
       </c>
       <c r="F111" t="n">
         <v>452</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="n">
+        <v>349</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>342</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2575,6 +2575,28 @@
         <v>265</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>296</v>
+      </c>
+      <c r="C113" t="n">
+        <v>123</v>
+      </c>
+      <c r="D113" t="n">
+        <v>20</v>
+      </c>
+      <c r="E113" t="n">
+        <v>2</v>
+      </c>
+      <c r="F113" t="n">
+        <v>315</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2586,7 +2608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4570,6 +4592,25 @@
       </c>
       <c r="F112" s="3" t="n">
         <v>342</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>195</v>
+      </c>
+      <c r="C113" t="n">
+        <v>135</v>
+      </c>
+      <c r="D113" t="n">
+        <v>37</v>
+      </c>
+      <c r="F113" t="n">
+        <v>258</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F113"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2597,6 +2597,28 @@
         <v>315</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n">
+        <v>313</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>335</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2608,7 +2630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F113"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4611,6 +4633,28 @@
       </c>
       <c r="F113" t="n">
         <v>258</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n">
+        <v>321</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2619,6 +2619,28 @@
         <v>335</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>245</v>
+      </c>
+      <c r="C115" t="n">
+        <v>97</v>
+      </c>
+      <c r="D115" t="n">
+        <v>26</v>
+      </c>
+      <c r="E115" t="n">
+        <v>4</v>
+      </c>
+      <c r="F115" t="n">
+        <v>208</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2630,7 +2652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4655,6 +4677,28 @@
       </c>
       <c r="F114" s="3" t="n">
         <v>226</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>233</v>
+      </c>
+      <c r="C115" t="n">
+        <v>94</v>
+      </c>
+      <c r="D115" t="n">
+        <v>25</v>
+      </c>
+      <c r="E115" t="n">
+        <v>4</v>
+      </c>
+      <c r="F115" t="n">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2641,6 +2641,18 @@
         <v>208</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n"/>
+      <c r="C116" s="3" t="n"/>
+      <c r="D116" s="3" t="n"/>
+      <c r="E116" s="3" t="n"/>
+      <c r="F116" s="3" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2652,7 +2664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4700,6 +4712,18 @@
       <c r="F115" t="n">
         <v>126</v>
       </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n"/>
+      <c r="C116" s="3" t="n"/>
+      <c r="D116" s="3" t="n"/>
+      <c r="E116" s="3" t="n"/>
+      <c r="F116" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2653,6 +2653,25 @@
       <c r="E116" s="3" t="n"/>
       <c r="F116" s="3" t="n"/>
     </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>91</v>
+      </c>
+      <c r="C117" t="n">
+        <v>25</v>
+      </c>
+      <c r="D117" t="n">
+        <v>5</v>
+      </c>
+      <c r="F117" t="n">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2664,7 +2683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4724,6 +4743,25 @@
       <c r="D116" s="3" t="n"/>
       <c r="E116" s="3" t="n"/>
       <c r="F116" s="3" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="n">
+        <v>52</v>
+      </c>
+      <c r="D117" t="n">
+        <v>12</v>
+      </c>
+      <c r="F117" t="n">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2672,6 +2672,28 @@
         <v>59</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>357</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2683,7 +2705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4761,6 +4783,26 @@
       </c>
       <c r="F117" t="n">
         <v>50</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>237</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E118" s="3" t="n"/>
+      <c r="F118" s="3" t="n">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2694,6 +2694,28 @@
         <v>357</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>208</v>
+      </c>
+      <c r="C119" t="n">
+        <v>85</v>
+      </c>
+      <c r="D119" t="n">
+        <v>24</v>
+      </c>
+      <c r="E119" t="n">
+        <v>6</v>
+      </c>
+      <c r="F119" t="n">
+        <v>235</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2705,7 +2727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4803,6 +4825,28 @@
       <c r="E118" s="3" t="n"/>
       <c r="F118" s="3" t="n">
         <v>150</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>400</v>
+      </c>
+      <c r="C119" t="n">
+        <v>118</v>
+      </c>
+      <c r="D119" t="n">
+        <v>28</v>
+      </c>
+      <c r="E119" t="n">
+        <v>20</v>
+      </c>
+      <c r="F119" t="n">
+        <v>281</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2716,6 +2716,28 @@
         <v>235</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="n">
+        <v>329</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>289</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2727,7 +2749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4847,6 +4869,26 @@
       </c>
       <c r="F119" t="n">
         <v>281</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E120" s="3" t="n"/>
+      <c r="F120" s="3" t="n">
+        <v>375</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2738,6 +2738,28 @@
         <v>289</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>311</v>
+      </c>
+      <c r="C121" t="n">
+        <v>94</v>
+      </c>
+      <c r="D121" t="n">
+        <v>32</v>
+      </c>
+      <c r="E121" t="n">
+        <v>5</v>
+      </c>
+      <c r="F121" t="n">
+        <v>251</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2749,7 +2771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4889,6 +4911,22 @@
       <c r="E120" s="3" t="n"/>
       <c r="F120" s="3" t="n">
         <v>375</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>254</v>
+      </c>
+      <c r="C121" t="n">
+        <v>92</v>
+      </c>
+      <c r="F121" t="n">
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2760,6 +2760,28 @@
         <v>251</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="n">
+        <v>310</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>287</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2771,7 +2793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4927,6 +4949,26 @@
       </c>
       <c r="F121" t="n">
         <v>212</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E122" s="3" t="n"/>
+      <c r="F122" s="3" t="n">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F122"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2782,6 +2782,22 @@
         <v>287</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>2</v>
+      </c>
+      <c r="C123" t="n">
+        <v>9</v>
+      </c>
+      <c r="F123" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2793,7 +2809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F122"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4969,6 +4985,13 @@
       <c r="E122" s="3" t="n"/>
       <c r="F122" s="3" t="n">
         <v>162</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2798,6 +2798,28 @@
         <v>5</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2809,7 +2831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4992,6 +5014,24 @@
         <is>
           <t>2026-09-27</t>
         </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D124" s="3" t="n"/>
+      <c r="E124" s="3" t="n"/>
+      <c r="F124" s="3" t="n">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2820,6 +2820,28 @@
         <v>78</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>355</v>
+      </c>
+      <c r="C125" t="n">
+        <v>106</v>
+      </c>
+      <c r="D125" t="n">
+        <v>22</v>
+      </c>
+      <c r="E125" t="n">
+        <v>5</v>
+      </c>
+      <c r="F125" t="n">
+        <v>332</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2831,7 +2853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5032,6 +5054,28 @@
       <c r="E124" s="3" t="n"/>
       <c r="F124" s="3" t="n">
         <v>54</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>78</v>
+      </c>
+      <c r="C125" t="n">
+        <v>104</v>
+      </c>
+      <c r="D125" t="n">
+        <v>5</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2</v>
+      </c>
+      <c r="F125" t="n">
+        <v>306</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2842,6 +2842,28 @@
         <v>332</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="n">
+        <v>277</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>273</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2853,7 +2875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5076,6 +5098,26 @@
       </c>
       <c r="F125" t="n">
         <v>306</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E126" s="3" t="n"/>
+      <c r="F126" s="3" t="n">
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2864,6 +2864,28 @@
         <v>273</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>295</v>
+      </c>
+      <c r="C127" t="n">
+        <v>139</v>
+      </c>
+      <c r="D127" t="n">
+        <v>12</v>
+      </c>
+      <c r="E127" t="n">
+        <v>4</v>
+      </c>
+      <c r="F127" t="n">
+        <v>411</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2875,7 +2897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5120,6 +5142,28 @@
         <v>268</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1024</v>
+      </c>
+      <c r="C127" t="n">
+        <v>179</v>
+      </c>
+      <c r="D127" t="n">
+        <v>139</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2</v>
+      </c>
+      <c r="F127" t="n">
+        <v>478</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5131,7 +5175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5941,12 +5985,12 @@
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>7509808E</t>
+          <t>7984894</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>LEDstrip LST01</t>
+          <t>LED-driver 10W</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
@@ -5958,7 +6002,7 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>7509809</t>
+          <t>7509808E</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
@@ -5975,7 +6019,7 @@
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>7509810</t>
+          <t>7509809</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -5992,12 +6036,12 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>1377790</t>
+          <t>7509810</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Monteringsclips DIN/vägg</t>
+          <t>LEDstrip LST01</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -6009,12 +6053,12 @@
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>1377791</t>
+          <t>1377790</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Monteringsdosa</t>
+          <t>Monteringsclips DIN/vägg</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
@@ -6026,12 +6070,12 @@
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>1377709</t>
+          <t>1377791</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Relä 2-pol 16A/13A mesh Bluetooth</t>
+          <t>Monteringsdosa</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -6043,12 +6087,12 @@
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>1307779</t>
+          <t>1377709</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>Rörelsevakt trådlös hörnmonterad</t>
+          <t>Relä 2-pol 16A/13A mesh Bluetooth</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
@@ -6060,12 +6104,12 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>1377740</t>
+          <t>1307779</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Smart plug On/Off, 16A, Mesh, Bluetooth</t>
+          <t>Rörelsevakt trådlös hörnmonterad</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
@@ -6077,7 +6121,7 @@
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>1377741</t>
+          <t>1377740</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -6094,12 +6138,12 @@
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>1893380</t>
+          <t>1377741</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Styrenhet för jalusier</t>
+          <t>Smart plug On/Off, 16A, Mesh, Bluetooth</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -6111,12 +6155,12 @@
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>1377722</t>
+          <t>1893380</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>Tryckknapp trådlös WPH-01-E</t>
+          <t>Styrenhet för jalusier</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
@@ -6128,7 +6172,7 @@
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>1377723</t>
+          <t>1377722</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
@@ -6145,12 +6189,12 @@
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>1377711</t>
+          <t>1377723</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Tryckknapp trådlös WPH-01-L</t>
+          <t>Tryckknapp trådlös WPH-01-E</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
@@ -6162,7 +6206,7 @@
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>1377712</t>
+          <t>1377711</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
@@ -6179,12 +6223,12 @@
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>1377721</t>
+          <t>1377712</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Tryckknapp trådlös WPH-01-S</t>
+          <t>Tryckknapp trådlös WPH-01-L</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
@@ -6196,7 +6240,7 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>1377724</t>
+          <t>1377721</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
@@ -6213,12 +6257,12 @@
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>1893384</t>
+          <t>1377724</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Tryckknapp trådlös, med pilar, WPH-01-A-xx</t>
+          <t>Tryckknapp trådlös WPH-01-S</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
@@ -6230,7 +6274,7 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>1893385</t>
+          <t>1893384</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
@@ -6247,7 +6291,7 @@
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>1893386</t>
+          <t>1893385</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
@@ -6264,7 +6308,7 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>1893387</t>
+          <t>1893386</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
@@ -6281,12 +6325,12 @@
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>1377708</t>
+          <t>1893387</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-E</t>
+          <t>Tryckknapp trådlös, med pilar, WPH-01-A-xx</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
@@ -6298,7 +6342,7 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>1377726</t>
+          <t>1377708</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
@@ -6315,12 +6359,12 @@
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>1377713</t>
+          <t>1377726</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-L</t>
+          <t>Trådlös vridratt WRT-01-E</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
@@ -6332,7 +6376,7 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>1377714</t>
+          <t>1377713</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
@@ -6349,12 +6393,12 @@
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>1377773</t>
+          <t>1377714</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-R</t>
+          <t>Trådlös vridratt WRT-01-L</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
@@ -6366,7 +6410,7 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>1377772</t>
+          <t>1377773</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
@@ -6383,12 +6427,12 @@
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>1377707</t>
+          <t>1377772</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>Trådlös vridratt WRT-01-S</t>
+          <t>Trådlös vridratt WRT-01-R</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
@@ -6400,7 +6444,7 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>1377727</t>
+          <t>1377707</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
@@ -6417,12 +6461,12 @@
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>1377737</t>
+          <t>1377727</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
+          <t>Trådlös vridratt WRT-01-S</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
@@ -6434,7 +6478,7 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>1377735</t>
+          <t>1377737</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
@@ -6451,12 +6495,12 @@
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>1377733</t>
+          <t>1377735</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-E</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
@@ -6468,7 +6512,7 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>1377734</t>
+          <t>1377733</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
@@ -6485,12 +6529,12 @@
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>1377736</t>
+          <t>1377734</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>Vridadapter Plejd för dosdimmer RTR-01-S</t>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-R</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
@@ -6502,15 +6546,32 @@
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
+          <t>1377736</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>Vridadapter Plejd för dosdimmer RTR-01-S</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>Övrigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
           <t>1377738</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>Vridadapter Plejd för dosdimmer RTR-01-S</t>
         </is>
       </c>
-      <c r="C81" s="11" t="inlineStr">
+      <c r="C82" s="11" t="inlineStr">
         <is>
           <t>Övrigt</t>
         </is>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2886,6 +2886,28 @@
         <v>411</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="n">
+        <v>312</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2897,7 +2919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5162,6 +5184,26 @@
       </c>
       <c r="F127" t="n">
         <v>478</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="n">
+        <v>327</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E128" s="3" t="n"/>
+      <c r="F128" s="3" t="n">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2908,6 +2908,28 @@
         <v>333</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>190</v>
+      </c>
+      <c r="C129" t="n">
+        <v>65</v>
+      </c>
+      <c r="D129" t="n">
+        <v>23</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" t="n">
+        <v>214</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2919,7 +2941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5204,6 +5226,28 @@
       <c r="E128" s="3" t="n"/>
       <c r="F128" s="3" t="n">
         <v>135</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>314</v>
+      </c>
+      <c r="C129" t="n">
+        <v>65</v>
+      </c>
+      <c r="D129" t="n">
+        <v>5</v>
+      </c>
+      <c r="E129" t="n">
+        <v>8</v>
+      </c>
+      <c r="F129" t="n">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2930,6 +2930,20 @@
         <v>214</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="n"/>
+      <c r="C130" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D130" s="3" t="n"/>
+      <c r="E130" s="3" t="n"/>
+      <c r="F130" s="3" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2941,7 +2955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5249,6 +5263,18 @@
       <c r="F129" t="n">
         <v>182</v>
       </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="n"/>
+      <c r="C130" s="3" t="n"/>
+      <c r="D130" s="3" t="n"/>
+      <c r="E130" s="3" t="n"/>
+      <c r="F130" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2944,6 +2944,25 @@
       <c r="E130" s="3" t="n"/>
       <c r="F130" s="3" t="n"/>
     </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>110</v>
+      </c>
+      <c r="C131" t="n">
+        <v>13</v>
+      </c>
+      <c r="D131" t="n">
+        <v>10</v>
+      </c>
+      <c r="F131" t="n">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2955,7 +2974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5275,6 +5294,22 @@
       <c r="D130" s="3" t="n"/>
       <c r="E130" s="3" t="n"/>
       <c r="F130" s="3" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>80</v>
+      </c>
+      <c r="C131" t="n">
+        <v>32</v>
+      </c>
+      <c r="F131" t="n">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2963,6 +2963,28 @@
         <v>84</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="n">
+        <v>302</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>369</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2974,7 +2996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5309,6 +5331,26 @@
       </c>
       <c r="F131" t="n">
         <v>50</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="n">
+        <v>385</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="D132" s="3" t="n"/>
+      <c r="E132" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>339</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2985,6 +2985,28 @@
         <v>369</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>366</v>
+      </c>
+      <c r="C133" t="n">
+        <v>128</v>
+      </c>
+      <c r="D133" t="n">
+        <v>35</v>
+      </c>
+      <c r="E133" t="n">
+        <v>2</v>
+      </c>
+      <c r="F133" t="n">
+        <v>309</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2996,7 +3018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5351,6 +5373,28 @@
       </c>
       <c r="F132" s="3" t="n">
         <v>339</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>196</v>
+      </c>
+      <c r="C133" t="n">
+        <v>97</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
+        <v>4</v>
+      </c>
+      <c r="F133" t="n">
+        <v>369</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F133"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3007,6 +3007,26 @@
         <v>309</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="n">
+        <v>383</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="E134" s="3" t="n"/>
+      <c r="F134" s="3" t="n">
+        <v>355</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3018,7 +3038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F133"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5395,6 +5415,28 @@
       </c>
       <c r="F133" t="n">
         <v>369</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>305</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3027,6 +3027,28 @@
         <v>355</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>334</v>
+      </c>
+      <c r="C135" t="n">
+        <v>95</v>
+      </c>
+      <c r="D135" t="n">
+        <v>23</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" t="n">
+        <v>345</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3038,7 +3060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5437,6 +5459,25 @@
       </c>
       <c r="F134" s="3" t="n">
         <v>305</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>437</v>
+      </c>
+      <c r="C135" t="n">
+        <v>97</v>
+      </c>
+      <c r="D135" t="n">
+        <v>36</v>
+      </c>
+      <c r="F135" t="n">
+        <v>544</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3049,6 +3049,28 @@
         <v>345</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>228</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3060,7 +3082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5478,6 +5500,26 @@
       </c>
       <c r="F135" t="n">
         <v>544</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E136" s="3" t="n"/>
+      <c r="F136" s="3" t="n">
+        <v>289</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3071,6 +3071,13 @@
         <v>228</v>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3082,7 +3089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5520,6 +5527,13 @@
       <c r="E136" s="3" t="n"/>
       <c r="F136" s="3" t="n">
         <v>289</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3078,6 +3078,26 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E138" s="3" t="n"/>
+      <c r="F138" s="3" t="n">
+        <v>188</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3089,7 +3109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5534,6 +5554,28 @@
         <is>
           <t>2026-10-11</t>
         </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>440</v>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3098,6 +3098,28 @@
         <v>188</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>297</v>
+      </c>
+      <c r="C139" t="n">
+        <v>119</v>
+      </c>
+      <c r="D139" t="n">
+        <v>28</v>
+      </c>
+      <c r="E139" t="n">
+        <v>32</v>
+      </c>
+      <c r="F139" t="n">
+        <v>408</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3109,7 +3131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5576,6 +5598,28 @@
       </c>
       <c r="F138" s="3" t="n">
         <v>203</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>192</v>
+      </c>
+      <c r="C139" t="n">
+        <v>94</v>
+      </c>
+      <c r="D139" t="n">
+        <v>84</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" t="n">
+        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3120,6 +3120,26 @@
         <v>408</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="n">
+        <v>212</v>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E140" s="3" t="n"/>
+      <c r="F140" s="3" t="n">
+        <v>242</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3131,7 +3151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5620,6 +5640,26 @@
       </c>
       <c r="F139" t="n">
         <v>249</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="n">
+        <v>254</v>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E140" s="3" t="n"/>
+      <c r="F140" s="3" t="n">
+        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3140,6 +3140,28 @@
         <v>242</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>345</v>
+      </c>
+      <c r="C141" t="n">
+        <v>83</v>
+      </c>
+      <c r="D141" t="n">
+        <v>37</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" t="n">
+        <v>333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3151,7 +3173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5660,6 +5682,28 @@
       <c r="E140" s="3" t="n"/>
       <c r="F140" s="3" t="n">
         <v>257</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>232</v>
+      </c>
+      <c r="C141" t="n">
+        <v>114</v>
+      </c>
+      <c r="D141" t="n">
+        <v>10</v>
+      </c>
+      <c r="E141" t="n">
+        <v>12</v>
+      </c>
+      <c r="F141" t="n">
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3162,6 +3162,28 @@
         <v>333</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="n">
+        <v>303</v>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>287</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3173,7 +3195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5704,6 +5726,26 @@
       </c>
       <c r="F141" t="n">
         <v>329</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="n">
+        <v>283</v>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" s="3" t="n"/>
+      <c r="F142" s="3" t="n">
+        <v>428</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3184,6 +3184,28 @@
         <v>287</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>333</v>
+      </c>
+      <c r="C143" t="n">
+        <v>87</v>
+      </c>
+      <c r="D143" t="n">
+        <v>24</v>
+      </c>
+      <c r="E143" t="n">
+        <v>3</v>
+      </c>
+      <c r="F143" t="n">
+        <v>322</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3195,7 +3217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5746,6 +5768,25 @@
       <c r="E142" s="3" t="n"/>
       <c r="F142" s="3" t="n">
         <v>428</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>126</v>
+      </c>
+      <c r="C143" t="n">
+        <v>115</v>
+      </c>
+      <c r="D143" t="n">
+        <v>3</v>
+      </c>
+      <c r="F143" t="n">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3206,6 +3206,24 @@
         <v>322</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D144" s="3" t="n"/>
+      <c r="E144" s="3" t="n"/>
+      <c r="F144" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3217,7 +3235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5788,6 +5806,18 @@
       <c r="F143" t="n">
         <v>135</v>
       </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="n"/>
+      <c r="C144" s="3" t="n"/>
+      <c r="D144" s="3" t="n"/>
+      <c r="E144" s="3" t="n"/>
+      <c r="F144" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3224,6 +3224,25 @@
         <v>7</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>49</v>
+      </c>
+      <c r="C145" t="n">
+        <v>25</v>
+      </c>
+      <c r="D145" t="n">
+        <v>6</v>
+      </c>
+      <c r="F145" t="n">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3235,7 +3254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5818,6 +5837,28 @@
       <c r="D144" s="3" t="n"/>
       <c r="E144" s="3" t="n"/>
       <c r="F144" s="3" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>49</v>
+      </c>
+      <c r="C145" t="n">
+        <v>11</v>
+      </c>
+      <c r="D145" t="n">
+        <v>3</v>
+      </c>
+      <c r="E145" t="n">
+        <v>8</v>
+      </c>
+      <c r="F145" t="n">
+        <v>88</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3243,6 +3243,28 @@
         <v>64</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="n">
+        <v>315</v>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>329</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3254,7 +3276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5858,6 +5880,28 @@
       </c>
       <c r="F145" t="n">
         <v>88</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="n">
+        <v>372</v>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3265,6 +3265,28 @@
         <v>329</v>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>343</v>
+      </c>
+      <c r="C147" t="n">
+        <v>101</v>
+      </c>
+      <c r="D147" t="n">
+        <v>26</v>
+      </c>
+      <c r="E147" t="n">
+        <v>6</v>
+      </c>
+      <c r="F147" t="n">
+        <v>330</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3276,7 +3298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5902,6 +5924,28 @@
       </c>
       <c r="F146" s="3" t="n">
         <v>280</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>222</v>
+      </c>
+      <c r="C147" t="n">
+        <v>115</v>
+      </c>
+      <c r="D147" t="n">
+        <v>7</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" t="n">
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3287,6 +3287,28 @@
         <v>330</v>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="n">
+        <v>375</v>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>352</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3298,7 +3320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5946,6 +5968,26 @@
       </c>
       <c r="F147" t="n">
         <v>327</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="n">
+        <v>423</v>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="E148" s="3" t="n"/>
+      <c r="F148" s="3" t="n">
+        <v>335</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3309,6 +3309,28 @@
         <v>352</v>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>343</v>
+      </c>
+      <c r="C149" t="n">
+        <v>100</v>
+      </c>
+      <c r="D149" t="n">
+        <v>23</v>
+      </c>
+      <c r="E149" t="n">
+        <v>16</v>
+      </c>
+      <c r="F149" t="n">
+        <v>395</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3320,7 +3342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5988,6 +6010,28 @@
       <c r="E148" s="3" t="n"/>
       <c r="F148" s="3" t="n">
         <v>335</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>276</v>
+      </c>
+      <c r="C149" t="n">
+        <v>95</v>
+      </c>
+      <c r="D149" t="n">
+        <v>130</v>
+      </c>
+      <c r="E149" t="n">
+        <v>4</v>
+      </c>
+      <c r="F149" t="n">
+        <v>205</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3331,6 +3331,60 @@
         <v>395</v>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E150" s="3" t="n"/>
+      <c r="F150" s="3" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" t="n">
+        <v>8</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D152" s="3" t="n"/>
+      <c r="E152" s="3" t="n"/>
+      <c r="F152" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3342,7 +3396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6032,6 +6086,55 @@
       </c>
       <c r="F149" t="n">
         <v>205</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="n">
+        <v>291</v>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E152" s="3" t="n"/>
+      <c r="F152" s="3" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:F153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3385,6 +3385,28 @@
         <v>7</v>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>363</v>
+      </c>
+      <c r="C153" t="n">
+        <v>170</v>
+      </c>
+      <c r="D153" t="n">
+        <v>40</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" t="n">
+        <v>343</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3396,7 +3418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:F153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6135,6 +6157,28 @@
       <c r="E152" s="3" t="n"/>
       <c r="F152" s="3" t="n">
         <v>19</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>266</v>
+      </c>
+      <c r="C153" t="n">
+        <v>67</v>
+      </c>
+      <c r="D153" t="n">
+        <v>40</v>
+      </c>
+      <c r="E153" t="n">
+        <v>10</v>
+      </c>
+      <c r="F153" t="n">
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F153"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3407,6 +3407,28 @@
         <v>343</v>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>153</v>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>393</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3418,7 +3440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F153"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6179,6 +6201,26 @@
       </c>
       <c r="F153" t="n">
         <v>236</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="n">
+        <v>578</v>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="E154" s="3" t="n"/>
+      <c r="F154" s="3" t="n">
+        <v>557</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F154"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3429,6 +3429,28 @@
         <v>393</v>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>368</v>
+      </c>
+      <c r="C155" t="n">
+        <v>113</v>
+      </c>
+      <c r="D155" t="n">
+        <v>26</v>
+      </c>
+      <c r="E155" t="n">
+        <v>17</v>
+      </c>
+      <c r="F155" t="n">
+        <v>283</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3440,7 +3462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F154"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6221,6 +6243,28 @@
       <c r="E154" s="3" t="n"/>
       <c r="F154" s="3" t="n">
         <v>557</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>169</v>
+      </c>
+      <c r="C155" t="n">
+        <v>97</v>
+      </c>
+      <c r="D155" t="n">
+        <v>33</v>
+      </c>
+      <c r="E155" t="n">
+        <v>4</v>
+      </c>
+      <c r="F155" t="n">
+        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3451,6 +3451,28 @@
         <v>283</v>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="n">
+        <v>414</v>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3462,7 +3484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6265,6 +6287,26 @@
       </c>
       <c r="F155" t="n">
         <v>263</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="n">
+        <v>333</v>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="E156" s="3" t="n"/>
+      <c r="F156" s="3" t="n">
+        <v>621</v>
       </c>
     </row>
   </sheetData>

--- a/data/ahlsell_plejd_inventory.xlsx
+++ b/data/ahlsell_plejd_inventory.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F156"/>
+  <dimension ref="A1:F157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3473,6 +3473,28 @@
         <v>296</v>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>210</v>
+      </c>
+      <c r="C157" t="n">
+        <v>118</v>
+      </c>
+      <c r="D157" t="n">
+        <v>27</v>
+      </c>
+      <c r="E157" t="n">
+        <v>22</v>
+      </c>
+      <c r="F157" t="n">
+        <v>225</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3484,7 +3506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F156"/>
+  <dimension ref="A1:F157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6307,6 +6329,28 @@
       <c r="E156" s="3" t="n"/>
       <c r="F156" s="3" t="n">
         <v>621</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>336</v>
+      </c>
+      <c r="C157" t="n">
+        <v>88</v>
+      </c>
+      <c r="D157" t="n">
+        <v>19</v>
+      </c>
+      <c r="E157" t="n">
+        <v>10</v>
+      </c>
+      <c r="F157" t="n">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
